--- a/E/WRCHOMP.xlsx
+++ b/E/WRCHOMP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t/>
   </si>
@@ -88,21 +88,15 @@
     <t>CHOMP MLOW PLAIN 50G</t>
   </si>
   <si>
-    <t>20137066</t>
-  </si>
-  <si>
-    <t>CHOMP MALOW RAISIN50</t>
+    <t>20137067</t>
+  </si>
+  <si>
+    <t>CHOMP MALOW STRAWB50</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20137067</t>
-  </si>
-  <si>
-    <t>CHOMP MALOW STRAWB50</t>
-  </si>
-  <si>
     <t>20137068</t>
   </si>
   <si>
@@ -139,19 +133,13 @@
     <t>CHOMP2 MALLOWPOP 16G</t>
   </si>
   <si>
-    <t>20133216</t>
-  </si>
-  <si>
-    <t>CHOMP TRIO PLAIN 21G</t>
+    <t>20133246</t>
+  </si>
+  <si>
+    <t>CHOMP TRIO RNBOW 21G</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>20133246</t>
-  </si>
-  <si>
-    <t>CHOMP TRIO RNBOW 21G</t>
   </si>
 </sst>
 </file>
@@ -544,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -767,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -787,7 +775,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -804,10 +792,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -815,42 +803,42 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,10 +852,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -884,52 +872,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
